--- a/data/source/xlsx/Locations.xlsx
+++ b/data/source/xlsx/Locations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>Repertory_ID</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Repertory_Locator</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -461,7 +466,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>tci_italia_centrale_1</t>
+          <t>bertarelli_1924</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>cart. 2, tra pp. 480–481</t>
         </is>
       </c>
     </row>
